--- a/sample_data/samp_var_list.xlsx
+++ b/sample_data/samp_var_list.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="253">
   <si>
     <t xml:space="preserve">Variable Number (VN)</t>
   </si>
@@ -745,6 +745,12 @@
   </si>
   <si>
     <t xml:space="preserve">Fe (mg/kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">na</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na (mg/kg)</t>
   </si>
   <si>
     <t xml:space="preserve">cu</t>
@@ -1118,7 +1124,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:R1001"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.63"/>
@@ -2428,14 +2434,22 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B118" s="2"/>
+      <c r="A118" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3"/>
       <c r="B119" s="2"/>
     </row>
     <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="2"/>
     </row>
     <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4"/>
@@ -2686,7 +2700,9 @@
     <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4"/>
     </row>
-    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="4"/>
+    </row>
     <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3483,6 +3499,7 @@
     <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1001" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3509,10 +3526,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3520,7 +3537,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3528,7 +3545,7 @@
         <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3536,28 +3553,28 @@
         <v>101</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B7" s="2"/>
     </row>
